--- a/events/Prague_2022_WC/Prague_2022_WC_start.xlsx
+++ b/events/Prague_2022_WC/Prague_2022_WC_start.xlsx
@@ -34249,6 +34249,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -38256,6 +38261,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X639" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -40223,6 +40233,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X668" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -41334,6 +41349,11 @@
       <c r="R684" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X684" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
